--- a/applications/SHIELD/Documentation/Syphilis Manager Data Overview_3.18.26.xlsx
+++ b/applications/SHIELD/Documentation/Syphilis Manager Data Overview_3.18.26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/zdansky1_jh_edu/Documents/Documents/JHEEM/code/jheem_analyses/applications/SHIELD/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1278" documentId="13_ncr:1_{460D6CD4-A812-4C2E-A51F-0C846BEEF02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D91253D-9B94-4100-AC66-CE01EA07D325}"/>
+  <xr:revisionPtr revIDLastSave="1279" documentId="13_ncr:1_{460D6CD4-A812-4C2E-A51F-0C846BEEF02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3C948E5-0FD4-4022-8E2B-8196722EC6A2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1057,7 +1057,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1109,7 +1109,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1409,6 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M96"/>
   <sheetFormatPr defaultColWidth="28.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1468,7 +1468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11"/>
       <c r="B2" s="12" t="s">
         <v>13</v>
@@ -1504,7 +1504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="12" t="s">
         <v>13</v>
@@ -1540,7 +1540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="12" t="s">
         <v>13</v>
@@ -1576,7 +1576,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
         <v>13</v>
@@ -1612,7 +1612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="12" t="s">
         <v>13</v>
@@ -1645,7 +1645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="30.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="12" t="s">
         <v>13</v>
@@ -1684,7 +1684,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="12" t="s">
         <v>13</v>
@@ -1723,7 +1723,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="12" t="s">
         <v>13</v>
@@ -1756,7 +1756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="12" t="s">
         <v>13</v>
@@ -1792,7 +1792,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="12" t="s">
         <v>13</v>
@@ -1828,7 +1828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="12" t="s">
         <v>13</v>
@@ -1864,7 +1864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="12" t="s">
         <v>13</v>
@@ -1900,7 +1900,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>13</v>
@@ -1936,7 +1936,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="12" t="s">
         <v>13</v>
@@ -1969,7 +1969,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="12" t="s">
         <v>13</v>
@@ -2005,7 +2005,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="12" t="s">
         <v>13</v>
@@ -2041,7 +2041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="12" t="s">
         <v>13</v>
@@ -2077,7 +2077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>58</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="12" t="s">
         <v>13</v>
@@ -2148,7 +2148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
         <v>13</v>
@@ -2181,7 +2181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="12" t="s">
         <v>13</v>
@@ -2217,7 +2217,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="12" t="s">
         <v>13</v>
@@ -2247,7 +2247,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="12" t="s">
         <v>13</v>
@@ -2286,7 +2286,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="12" t="s">
         <v>13</v>
@@ -2325,7 +2325,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12" t="s">
         <v>13</v>
@@ -2364,7 +2364,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="12" t="s">
         <v>13</v>
@@ -2400,7 +2400,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="12" t="s">
         <v>13</v>
@@ -2430,7 +2430,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="12" t="s">
         <v>13</v>
@@ -2460,7 +2460,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="12" t="s">
         <v>13</v>
@@ -2499,7 +2499,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="12" t="s">
         <v>13</v>
@@ -2535,7 +2535,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
         <v>13</v>
@@ -2571,7 +2571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="12" t="s">
         <v>13</v>
@@ -2607,7 +2607,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="12" t="s">
         <v>13</v>
@@ -2640,7 +2640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" s="16" customFormat="1" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
         <v>81</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" s="16" customFormat="1" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
       <c r="B36" s="15" t="s">
         <v>82</v>
@@ -2716,7 +2716,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" s="16" customFormat="1" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="24"/>
       <c r="B37" s="15" t="s">
         <v>82</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="M37" s="13"/>
     </row>
-    <row r="38" spans="1:13" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" s="16" customFormat="1" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A38" s="24"/>
       <c r="B38" s="15" t="s">
         <v>82</v>
@@ -2790,7 +2790,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A39" s="24"/>
       <c r="B39" s="15" t="s">
         <v>82</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="M39" s="13"/>
     </row>
-    <row r="40" spans="1:13" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" s="16" customFormat="1" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A40" s="24"/>
       <c r="B40" s="15" t="s">
         <v>82</v>
@@ -2862,7 +2862,7 @@
       <c r="L40" s="14"/>
       <c r="M40" s="13"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A41" s="24"/>
       <c r="B41" s="15" t="s">
         <v>82</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="M41" s="13"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A42" s="24"/>
       <c r="B42" s="15" t="s">
         <v>82</v>
@@ -2934,7 +2934,7 @@
       <c r="L42" s="14"/>
       <c r="M42" s="13"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
       <c r="B43" s="15" t="s">
         <v>82</v>
@@ -2969,7 +2969,7 @@
       <c r="L43" s="14"/>
       <c r="M43" s="13"/>
     </row>
-    <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A44" s="24"/>
       <c r="B44" s="15" t="s">
         <v>82</v>
@@ -3004,7 +3004,7 @@
       <c r="L44" s="14"/>
       <c r="M44" s="13"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="15" t="s">
         <v>82</v>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M45" s="13"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="15" t="s">
         <v>82</v>
@@ -3074,7 +3074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A47" s="24"/>
       <c r="B47" s="15" t="s">
         <v>82</v>
@@ -3107,7 +3107,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A48" s="24"/>
       <c r="B48" s="15" t="s">
         <v>82</v>
@@ -3140,7 +3140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24"/>
       <c r="B49" s="15" t="s">
         <v>82</v>
@@ -3178,7 +3178,7 @@
       <c r="B50" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" t="s">
         <v>102</v>
       </c>
       <c r="D50" t="s">
@@ -3206,7 +3206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="24"/>
       <c r="B51" s="15" t="s">
         <v>82</v>
@@ -3239,7 +3239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="24"/>
       <c r="B52" s="15" t="s">
         <v>82</v>
@@ -3272,7 +3272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="24"/>
       <c r="B53" s="15" t="s">
         <v>82</v>
@@ -3305,7 +3305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="24"/>
       <c r="B54" s="15" t="s">
         <v>82</v>
@@ -3341,7 +3341,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="24"/>
       <c r="B55" s="15" t="s">
         <v>82</v>
@@ -3380,7 +3380,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="23" t="s">
         <v>122</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="23"/>
       <c r="B57" s="17" t="s">
         <v>123</v>
@@ -3454,7 +3454,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="23"/>
       <c r="B58" s="17" t="s">
         <v>123</v>
@@ -3487,7 +3487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="23"/>
       <c r="B59" s="17" t="s">
         <v>123</v>
@@ -3520,7 +3520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="23"/>
       <c r="B60" s="17" t="s">
         <v>123</v>
@@ -3556,7 +3556,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="23"/>
       <c r="B61" s="17" t="s">
         <v>123</v>
@@ -3592,7 +3592,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="23"/>
       <c r="B62" s="17" t="s">
         <v>123</v>
@@ -3628,7 +3628,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="23"/>
       <c r="B63" s="17" t="s">
         <v>123</v>
@@ -3658,7 +3658,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="23"/>
       <c r="B64" s="17" t="s">
         <v>123</v>
@@ -3691,7 +3691,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="23"/>
       <c r="B65" s="17" t="s">
         <v>123</v>
@@ -3727,7 +3727,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="23"/>
       <c r="B66" s="17" t="s">
         <v>123</v>
@@ -3763,7 +3763,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="23"/>
       <c r="B67" s="17" t="s">
         <v>123</v>
@@ -3796,7 +3796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="23"/>
       <c r="B68" s="17" t="s">
         <v>123</v>
@@ -3829,7 +3829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="23"/>
       <c r="B69" s="17" t="s">
         <v>123</v>
@@ -3865,7 +3865,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="23"/>
       <c r="B70" s="17" t="s">
         <v>123</v>
@@ -3898,7 +3898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="23"/>
       <c r="B71" s="17" t="s">
         <v>123</v>
@@ -3934,7 +3934,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="23"/>
       <c r="B72" s="18" t="s">
         <v>156</v>
@@ -3973,7 +3973,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="23"/>
       <c r="B73" s="18" t="s">
         <v>156</v>
@@ -4012,7 +4012,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="13" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" s="13" customFormat="1" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="23"/>
       <c r="B74" s="18" t="s">
         <v>156</v>
@@ -4048,7 +4048,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="13" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" s="13" customFormat="1" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="23"/>
       <c r="B75" s="18" t="s">
         <v>156</v>
@@ -4084,7 +4084,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
         <v>173</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="24"/>
       <c r="B77" s="15" t="s">
         <v>82</v>
@@ -4164,7 +4164,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="24"/>
       <c r="B78" s="15" t="s">
         <v>82</v>
@@ -4197,7 +4197,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="24"/>
       <c r="B79" s="15" t="s">
         <v>82</v>
@@ -4233,7 +4233,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="24"/>
       <c r="B80" s="15" t="s">
         <v>82</v>
@@ -4272,7 +4272,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="24"/>
       <c r="B81" s="15" t="s">
         <v>82</v>
@@ -4311,7 +4311,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="24"/>
       <c r="B82" s="15" t="s">
         <v>82</v>
@@ -4350,7 +4350,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="24"/>
       <c r="B83" s="15" t="s">
         <v>82</v>
@@ -4389,7 +4389,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="24"/>
       <c r="B84" s="15" t="s">
         <v>82</v>
@@ -4428,7 +4428,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="24"/>
       <c r="B85" s="15" t="s">
         <v>82</v>
@@ -4467,7 +4467,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="24"/>
       <c r="B86" s="15" t="s">
         <v>82</v>
@@ -4506,7 +4506,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="24"/>
       <c r="B87" s="15" t="s">
         <v>82</v>
@@ -4545,7 +4545,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="24"/>
       <c r="B88" s="15" t="s">
         <v>82</v>
@@ -4581,7 +4581,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="24"/>
       <c r="B89" s="15" t="s">
         <v>82</v>
@@ -4617,7 +4617,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="86.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="24"/>
       <c r="B90" s="15" t="s">
         <v>82</v>
@@ -4653,7 +4653,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="86.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="24"/>
       <c r="B91" s="15" t="s">
         <v>82</v>
@@ -4686,7 +4686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="24"/>
       <c r="B92" s="15" t="s">
         <v>82</v>
@@ -4722,7 +4722,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
         <v>214</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22"/>
       <c r="B94" s="20" t="s">
         <v>215</v>
@@ -4796,7 +4796,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="22"/>
       <c r="B95" s="20" t="s">
         <v>215</v>
@@ -4832,7 +4832,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="22"/>
       <c r="B96" s="20" t="s">
         <v>215</v>
@@ -4869,7 +4869,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M96" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="census.cdc.wonder.births.deaths"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="A93:A96"/>
     <mergeCell ref="A56:A75"/>
